--- a/Excel/DungeonTransferConfig.xlsx
+++ b/Excel/DungeonTransferConfig.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28695" windowHeight="14085"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="DungeonTransferProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="255">
   <si>
     <t>Id</t>
   </si>
@@ -37,6 +50,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Name_EN</t>
+  </si>
+  <si>
     <t>MapID</t>
   </si>
   <si>
@@ -61,6 +77,9 @@
     <t>绿林小镇</t>
   </si>
   <si>
+    <t>Greenwood Town</t>
+  </si>
+  <si>
     <t>720,127,-257</t>
   </si>
   <si>
@@ -70,6 +89,9 @@
     <t>矿洞一层</t>
   </si>
   <si>
+    <t>Cave Level 1</t>
+  </si>
+  <si>
     <t>15200,2930,-6764</t>
   </si>
   <si>
@@ -79,6 +101,9 @@
     <t>矿洞二层</t>
   </si>
   <si>
+    <t>Cave Level 2</t>
+  </si>
+  <si>
     <t>16292,2912,-7514</t>
   </si>
   <si>
@@ -88,6 +113,9 @@
     <t>绿林郊外</t>
   </si>
   <si>
+    <t>Green Outskirts</t>
+  </si>
+  <si>
     <t>15400,2902,-6336</t>
   </si>
   <si>
@@ -97,6 +125,9 @@
     <t>绿林深处</t>
   </si>
   <si>
+    <t>Deep Green Woods</t>
+  </si>
+  <si>
     <t>14400,2900,-7200</t>
   </si>
   <si>
@@ -106,6 +137,9 @@
     <t>地下洞穴</t>
   </si>
   <si>
+    <t>Underground Cave</t>
+  </si>
+  <si>
     <t>16800,2910,-6970</t>
   </si>
   <si>
@@ -115,6 +149,9 @@
     <t>石墓一层</t>
   </si>
   <si>
+    <t>Stone Tomb 1</t>
+  </si>
+  <si>
     <t>14300,2910,-4400</t>
   </si>
   <si>
@@ -124,6 +161,9 @@
     <t>石墓二层</t>
   </si>
   <si>
+    <t>Stone Tomb 2</t>
+  </si>
+  <si>
     <t>14400,2910,-4300</t>
   </si>
   <si>
@@ -133,6 +173,9 @@
     <t>矿洞一层去绿林小镇</t>
   </si>
   <si>
+    <t>Cave Level 1 to Greenwood Town</t>
+  </si>
+  <si>
     <t>7738,-100,-5766</t>
   </si>
   <si>
@@ -142,6 +185,9 @@
     <t>矿洞二层去矿洞一层</t>
   </si>
   <si>
+    <t>Cave Level 2 to Cave Level 1</t>
+  </si>
+  <si>
     <t>15819,2914,3879</t>
   </si>
   <si>
@@ -151,6 +197,9 @@
     <t>绿林深处去绿林郊外</t>
   </si>
   <si>
+    <t>Deep Green Woods to Green Outskirts</t>
+  </si>
+  <si>
     <t>25700,2910,-3300</t>
   </si>
   <si>
@@ -160,6 +209,9 @@
     <t>地下洞穴去石墓二层</t>
   </si>
   <si>
+    <t>Underground Cave to Stone Tomb 2</t>
+  </si>
+  <si>
     <t>20300,2910,-4900</t>
   </si>
   <si>
@@ -169,6 +221,9 @@
     <t>石墓一层去绿林郊外</t>
   </si>
   <si>
+    <t>Stone Tomb 1 to Green Outskirts</t>
+  </si>
+  <si>
     <t>26100,2910,-7300</t>
   </si>
   <si>
@@ -178,6 +233,9 @@
     <t>石墓二层去石墓一层</t>
   </si>
   <si>
+    <t>Stone Tomb 2 to Stone Tomb 1</t>
+  </si>
+  <si>
     <t>24910,2911,-4356</t>
   </si>
   <si>
@@ -187,12 +245,18 @@
     <t>热荒沙漠</t>
   </si>
   <si>
+    <t>Hot Desert</t>
+  </si>
+  <si>
     <t>14532,2895,-5271</t>
   </si>
   <si>
     <t>绿洲小径</t>
   </si>
   <si>
+    <t>Oasis Path</t>
+  </si>
+  <si>
     <t>15259,2895,-9335</t>
   </si>
   <si>
@@ -202,6 +266,9 @@
     <t>遗忘废墟</t>
   </si>
   <si>
+    <t>Forgotten Ruins</t>
+  </si>
+  <si>
     <t>15756,2895,-7717</t>
   </si>
   <si>
@@ -211,6 +278,9 @@
     <t>地牢一层</t>
   </si>
   <si>
+    <t>Dungeon 1</t>
+  </si>
+  <si>
     <t>14613,2895,-7096</t>
   </si>
   <si>
@@ -220,6 +290,9 @@
     <t>地牢二层</t>
   </si>
   <si>
+    <t>Dungeon 2</t>
+  </si>
+  <si>
     <t>21779,3066,-2383</t>
   </si>
   <si>
@@ -229,6 +302,9 @@
     <t>绿洲小径去热荒沙漠</t>
   </si>
   <si>
+    <t>Oasis Path to Hot Desert</t>
+  </si>
+  <si>
     <t>2139,2895,-7394</t>
   </si>
   <si>
@@ -238,6 +314,9 @@
     <t>遗忘废墟去绿洲小径</t>
   </si>
   <si>
+    <t>Forgotten Ruins to Oasis Path</t>
+  </si>
+  <si>
     <t>5935,2895,-5220</t>
   </si>
   <si>
@@ -247,6 +326,9 @@
     <t>地牢一层去热荒沙漠</t>
   </si>
   <si>
+    <t>Dungeon 1 to Hot Desert</t>
+  </si>
+  <si>
     <t>13404,2895,-7275</t>
   </si>
   <si>
@@ -256,6 +338,9 @@
     <t>地牢二层去地牢一层</t>
   </si>
   <si>
+    <t>Dungeon 2 to Dungeon 1</t>
+  </si>
+  <si>
     <t>18734,2814,3021</t>
   </si>
   <si>
@@ -265,12 +350,18 @@
     <t>冰封城镇</t>
   </si>
   <si>
+    <t>Ice Town</t>
+  </si>
+  <si>
     <t>15369,2911,-4216</t>
   </si>
   <si>
     <t>冰封森林</t>
   </si>
   <si>
+    <t>Ice Forest</t>
+  </si>
+  <si>
     <t>13898,2905,-4124</t>
   </si>
   <si>
@@ -280,6 +371,9 @@
     <t>冰封堡垒</t>
   </si>
   <si>
+    <t>Ice Fort</t>
+  </si>
+  <si>
     <t>14983,2910,-5997</t>
   </si>
   <si>
@@ -289,6 +383,9 @@
     <t>千针叶林</t>
   </si>
   <si>
+    <t>Pine Forest</t>
+  </si>
+  <si>
     <t>14000,2905,-4277</t>
   </si>
   <si>
@@ -298,6 +395,9 @@
     <t>冰封之路</t>
   </si>
   <si>
+    <t>Ice Road</t>
+  </si>
+  <si>
     <t>14372,2911,-7262</t>
   </si>
   <si>
@@ -307,6 +407,9 @@
     <t>冰封魔穴</t>
   </si>
   <si>
+    <t>Ice Cave</t>
+  </si>
+  <si>
     <t>14883,3467,-7290</t>
   </si>
   <si>
@@ -316,6 +419,9 @@
     <t>冰封森林去冰封城镇</t>
   </si>
   <si>
+    <t>Ice Forest to Ice Town</t>
+  </si>
+  <si>
     <t>21591,2911,-5370</t>
   </si>
   <si>
@@ -325,6 +431,9 @@
     <t>冰封堡垒去冰封森林</t>
   </si>
   <si>
+    <t>Ice Fort to Ice Forest</t>
+  </si>
+  <si>
     <t>23656,3048,-1746</t>
   </si>
   <si>
@@ -334,6 +443,9 @@
     <t>千针叶林去冰封森林</t>
   </si>
   <si>
+    <t>Pine Forest to Ice Forest</t>
+  </si>
+  <si>
     <t>24258,3048,-1821</t>
   </si>
   <si>
@@ -343,6 +455,9 @@
     <t>冰封之路去千针叶林</t>
   </si>
   <si>
+    <t>Ice Road to Pine Forest</t>
+  </si>
+  <si>
     <t>16698,2910,3021</t>
   </si>
   <si>
@@ -352,6 +467,9 @@
     <t>冰封魔穴去冰封之路</t>
   </si>
   <si>
+    <t>Ice Cave to Ice Road</t>
+  </si>
+  <si>
     <t>25092,3010,-4487</t>
   </si>
   <si>
@@ -361,6 +479,9 @@
     <t>冰封之路去冰封魔穴</t>
   </si>
   <si>
+    <t>Ice Road to Ice Cave</t>
+  </si>
+  <si>
     <t>14870,3466,-7600</t>
   </si>
   <si>
@@ -370,12 +491,18 @@
     <t>暮色城镇</t>
   </si>
   <si>
+    <t>Twilight Town</t>
+  </si>
+  <si>
     <t>18834,2910,-4755</t>
   </si>
   <si>
     <t>暮色郊外</t>
   </si>
   <si>
+    <t>Twilight Outskirts</t>
+  </si>
+  <si>
     <t>17650,2910,-7510</t>
   </si>
   <si>
@@ -385,6 +512,9 @@
     <t>暮色森林</t>
   </si>
   <si>
+    <t>Twilight Forest</t>
+  </si>
+  <si>
     <t>17670,2911,-7520</t>
   </si>
   <si>
@@ -394,6 +524,9 @@
     <t>暮色矿洞一层</t>
   </si>
   <si>
+    <t>Twilight Mine 1</t>
+  </si>
+  <si>
     <t>25645,2910,-6362</t>
   </si>
   <si>
@@ -403,6 +536,9 @@
     <t>暮色矿洞二层</t>
   </si>
   <si>
+    <t>Twilight Mine 2</t>
+  </si>
+  <si>
     <t>14301,2910,2212</t>
   </si>
   <si>
@@ -412,6 +548,9 @@
     <t>裂石峡谷</t>
   </si>
   <si>
+    <t>Crack Stone Canyon</t>
+  </si>
+  <si>
     <t>14611,2911,-2951</t>
   </si>
   <si>
@@ -421,6 +560,9 @@
     <t>地狱裂谷</t>
   </si>
   <si>
+    <t>Hell Rift</t>
+  </si>
+  <si>
     <t>24409,2910,-11440</t>
   </si>
   <si>
@@ -430,6 +572,9 @@
     <t>暮色郊外去暮色城镇</t>
   </si>
   <si>
+    <t>Twilight Outskirts to Twilight Town</t>
+  </si>
+  <si>
     <t>22823,2910,-4349</t>
   </si>
   <si>
@@ -439,6 +584,9 @@
     <t>裂石峡谷去暮色城镇</t>
   </si>
   <si>
+    <t>Crack Stone Canyon to Twilight Town</t>
+  </si>
+  <si>
     <t>22343,2910,2283</t>
   </si>
   <si>
@@ -448,6 +596,9 @@
     <t>暮色矿洞去暮色森林</t>
   </si>
   <si>
+    <t>Twilight Mine to Twilight Forest</t>
+  </si>
+  <si>
     <t>15969,2911,-1212</t>
   </si>
   <si>
@@ -457,6 +608,9 @@
     <t>暮色矿洞二层去暮色矿洞一层</t>
   </si>
   <si>
+    <t>Twilight Mine 2 to Twilight Mine 1</t>
+  </si>
+  <si>
     <t>15161,2910,-5520</t>
   </si>
   <si>
@@ -466,6 +620,9 @@
     <t>地狱裂谷去裂石峡谷</t>
   </si>
   <si>
+    <t>Hell Rift to Crack Stone Canyon</t>
+  </si>
+  <si>
     <t>28843,2911,-6720</t>
   </si>
   <si>
@@ -475,6 +632,9 @@
     <t>暮色森林去郊外</t>
   </si>
   <si>
+    <t>Twilight Forest to Outskirts</t>
+  </si>
+  <si>
     <t>20397,2910,3676</t>
   </si>
   <si>
@@ -484,12 +644,18 @@
     <t>黑暗小镇</t>
   </si>
   <si>
+    <t>Dark Town</t>
+  </si>
+  <si>
     <t>231,2910,-1310</t>
   </si>
   <si>
     <t>诡异小径</t>
   </si>
   <si>
+    <t>Weird Path</t>
+  </si>
+  <si>
     <t>15993,2910,-7254</t>
   </si>
   <si>
@@ -499,6 +665,9 @@
     <t>腐蚀之地</t>
   </si>
   <si>
+    <t>Rotten Land</t>
+  </si>
+  <si>
     <t>15110,2910,10008</t>
   </si>
   <si>
@@ -508,6 +677,9 @@
     <t>黑暗走廊一层</t>
   </si>
   <si>
+    <t>Dark Hall 1</t>
+  </si>
+  <si>
     <t>14457,2910,-7165</t>
   </si>
   <si>
@@ -517,6 +689,9 @@
     <t>黑暗走廊二层</t>
   </si>
   <si>
+    <t>Dark Hall 2</t>
+  </si>
+  <si>
     <t>3289,2814,22929</t>
   </si>
   <si>
@@ -526,6 +701,9 @@
     <t>黑暗走廊三层</t>
   </si>
   <si>
+    <t>Dark Hall 3</t>
+  </si>
+  <si>
     <t>38905,2910,14113</t>
   </si>
   <si>
@@ -535,6 +713,9 @@
     <t>黑暗之心</t>
   </si>
   <si>
+    <t>Dark Heart</t>
+  </si>
+  <si>
     <t>38443,2910,13759</t>
   </si>
   <si>
@@ -544,6 +725,9 @@
     <t>诡异小径去黑暗小镇</t>
   </si>
   <si>
+    <t>Weird Path to Dark Town</t>
+  </si>
+  <si>
     <t>7832,2910,-6881</t>
   </si>
   <si>
@@ -553,6 +737,9 @@
     <t>腐蚀之地去诡异小径</t>
   </si>
   <si>
+    <t>Rotten Land to Weird Path</t>
+  </si>
+  <si>
     <t>13618,2910,6375</t>
   </si>
   <si>
@@ -562,6 +749,9 @@
     <t>黑暗走廊一层去腐蚀之地</t>
   </si>
   <si>
+    <t>Dark Hall 1 to Rotten Land</t>
+  </si>
+  <si>
     <t>14432,2910,-6764</t>
   </si>
   <si>
@@ -571,6 +761,9 @@
     <t>黑暗走廊二层去一层</t>
   </si>
   <si>
+    <t>Dark Hall 2 to 1</t>
+  </si>
+  <si>
     <t>38484,2910,13914</t>
   </si>
   <si>
@@ -580,6 +773,9 @@
     <t>黑暗走廊三层去二层</t>
   </si>
   <si>
+    <t>Dark Hall 3 to 2</t>
+  </si>
+  <si>
     <t>-5260,2910,-7262</t>
   </si>
   <si>
@@ -587,6 +783,9 @@
   </si>
   <si>
     <t>黑暗之心去黑暗走廊三层</t>
+  </si>
+  <si>
+    <t>Dark Heart to Dark Hall 3</t>
   </si>
   <si>
     <t>6724,2910,-8579</t>
@@ -598,14 +797,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -634,15 +833,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -656,75 +857,23 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -740,30 +889,23 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -779,7 +921,57 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -806,7 +998,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -818,37 +1064,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -860,7 +1094,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -872,13 +1112,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -890,79 +1124,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -980,13 +1142,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1069,17 +1261,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1099,13 +1294,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1121,184 +1335,162 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1313,19 +1505,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -1340,57 +1532,62 @@
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1679,20 +1876,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:R66"/>
+  <dimension ref="C3:S66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
-    <col min="4" max="6" width="28.625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="28.375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="28.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="40.5" style="1" customWidth="1"/>
+    <col min="6" max="7" width="28.625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="28.375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8">
+    <row r="3" spans="3:9">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1700,19 +1899,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:8">
+    <row r="4" spans="3:9">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1731,2709 +1933,2898 @@
       <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="3:8">
+      <c r="I4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9">
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8">
+        <v>14</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9">
       <c r="C6" s="3">
         <v>1001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="4">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="4">
         <v>10001</v>
       </c>
-      <c r="F6" s="4">
+      <c r="G6" s="4">
         <v>1</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="3:18">
+      <c r="H6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="3:19">
       <c r="C7" s="3">
         <v>1002</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="D7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="6">
         <v>10002</v>
       </c>
-      <c r="F7" s="7">
+      <c r="G7" s="6">
         <v>1</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="H7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="1">
         <v>15200</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>2930</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>-6764</v>
       </c>
-      <c r="N7" s="1">
-        <f>J7</f>
+      <c r="O7" s="1">
+        <f>K7</f>
         <v>15200</v>
       </c>
-      <c r="O7" s="1">
-        <f>IF(K7&lt;2800,2910,K7)</f>
+      <c r="P7" s="1">
+        <f>IF(L7&lt;2800,2910,L7)</f>
         <v>2930</v>
       </c>
-      <c r="P7" s="1">
-        <f>L7</f>
+      <c r="Q7" s="1">
+        <f>M7</f>
         <v>-6764</v>
       </c>
-      <c r="R7" s="1" t="str">
-        <f>N7&amp;","&amp;O7&amp;","&amp;P7</f>
+      <c r="S7" s="1" t="str">
+        <f>O7&amp;","&amp;P7&amp;","&amp;Q7</f>
         <v>15200,2930,-6764</v>
       </c>
     </row>
-    <row r="8" spans="3:18">
+    <row r="8" spans="3:19">
       <c r="C8" s="3">
         <v>1003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="4">
+        <v>23</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="4">
         <v>10003</v>
       </c>
-      <c r="F8" s="4">
+      <c r="G8" s="4">
         <v>5</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="H8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="1">
         <v>16292</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>2812</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>-7514</v>
       </c>
-      <c r="N8" s="1">
-        <f t="shared" ref="N8:N66" si="0">J8</f>
+      <c r="O8" s="1">
+        <f t="shared" ref="O8:O66" si="0">K8</f>
         <v>16292</v>
       </c>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:O66" si="1">IF(K8&lt;2800,2910,K8)</f>
+      <c r="P8" s="1">
+        <f t="shared" ref="P8:P66" si="1">IF(L8&lt;2800,2910,L8)</f>
         <v>2812</v>
       </c>
-      <c r="P8" s="1">
-        <f t="shared" ref="P8:P66" si="2">L8</f>
+      <c r="Q8" s="1">
+        <f t="shared" ref="Q8:Q66" si="2">M8</f>
         <v>-7514</v>
       </c>
-      <c r="R8" s="1" t="str">
-        <f t="shared" ref="R8:R66" si="3">N8&amp;","&amp;O8&amp;","&amp;P8</f>
+      <c r="S8" s="1" t="str">
+        <f t="shared" ref="S8:S66" si="3">O8&amp;","&amp;P8&amp;","&amp;Q8</f>
         <v>16292,2812,-7514</v>
       </c>
     </row>
-    <row r="9" spans="3:18">
+    <row r="9" spans="3:19">
       <c r="C9" s="3">
         <v>1004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="4">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="4">
         <v>10004</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G9" s="4">
         <v>1</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="H9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="1">
         <v>15400</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>2800</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>-6336</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <f t="shared" si="1"/>
         <v>2800</v>
       </c>
-      <c r="P9" s="1">
+      <c r="Q9" s="1">
         <f t="shared" si="2"/>
         <v>-6336</v>
       </c>
-      <c r="R9" s="1" t="str">
+      <c r="S9" s="1" t="str">
         <f t="shared" si="3"/>
         <v>15400,2800,-6336</v>
       </c>
     </row>
-    <row r="10" spans="3:18">
+    <row r="10" spans="3:19">
       <c r="C10" s="3">
         <v>1005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="4">
+        <v>31</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="4">
         <v>10005</v>
       </c>
-      <c r="F10" s="4">
+      <c r="G10" s="4">
         <v>5</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="H10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="1">
         <v>14400</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>2800</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <v>-7200</v>
       </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <f t="shared" si="0"/>
         <v>14400</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <f t="shared" si="1"/>
         <v>2800</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <f t="shared" si="2"/>
         <v>-7200</v>
       </c>
-      <c r="R10" s="1" t="str">
+      <c r="S10" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14400,2800,-7200</v>
       </c>
     </row>
-    <row r="11" spans="3:18">
+    <row r="11" spans="3:19">
       <c r="C11" s="3">
         <v>1006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="4">
+        <v>35</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="4">
         <v>10006</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="4">
         <v>12</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="H11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="1">
         <v>16800</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>2791</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>-6970</v>
       </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
         <f t="shared" si="0"/>
         <v>16800</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P11" s="1">
+      <c r="Q11" s="1">
         <f t="shared" si="2"/>
         <v>-6970</v>
       </c>
-      <c r="R11" s="1" t="str">
+      <c r="S11" s="1" t="str">
         <f t="shared" si="3"/>
         <v>16800,2910,-6970</v>
       </c>
     </row>
-    <row r="12" spans="3:18">
+    <row r="12" spans="3:19">
       <c r="C12" s="3">
         <v>1007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="4">
+        <v>39</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="4">
         <v>10007</v>
       </c>
-      <c r="F12" s="4">
+      <c r="G12" s="4">
         <v>8</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="1">
+      <c r="H12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="1">
         <v>14300</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>2800</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <v>-4400</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <f t="shared" si="0"/>
         <v>14300</v>
       </c>
-      <c r="O12" s="1">
+      <c r="P12" s="1">
         <f t="shared" si="1"/>
         <v>2800</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <f t="shared" si="2"/>
         <v>-4400</v>
       </c>
-      <c r="R12" s="1" t="str">
+      <c r="S12" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14300,2800,-4400</v>
       </c>
     </row>
-    <row r="13" spans="3:18">
+    <row r="13" spans="3:19">
       <c r="C13" s="3">
         <v>1008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="4">
+        <v>43</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="4">
         <v>10008</v>
       </c>
-      <c r="F13" s="4">
+      <c r="G13" s="4">
         <v>1</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="H13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="1">
         <v>14400</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>2800</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <v>-4300</v>
       </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
         <f t="shared" si="0"/>
         <v>14400</v>
       </c>
-      <c r="O13" s="1">
+      <c r="P13" s="1">
         <f t="shared" si="1"/>
         <v>2800</v>
       </c>
-      <c r="P13" s="1">
+      <c r="Q13" s="1">
         <f t="shared" si="2"/>
         <v>-4300</v>
       </c>
-      <c r="R13" s="1" t="str">
+      <c r="S13" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14400,2800,-4300</v>
       </c>
     </row>
-    <row r="14" spans="3:18">
+    <row r="14" spans="3:19">
       <c r="C14" s="3">
         <v>1009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="4">
+        <v>47</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="4">
         <v>10001</v>
       </c>
-      <c r="F14" s="4">
+      <c r="G14" s="4">
         <v>1</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="H14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14" s="1">
+        <v>49</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="1">
         <v>7670</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>2938</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <v>-7206</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <f t="shared" si="0"/>
         <v>7670</v>
       </c>
-      <c r="O14" s="1">
+      <c r="P14" s="1">
         <f t="shared" si="1"/>
         <v>2938</v>
       </c>
-      <c r="P14" s="1">
+      <c r="Q14" s="1">
         <f t="shared" si="2"/>
         <v>-7206</v>
       </c>
-      <c r="R14" s="1" t="str">
+      <c r="S14" s="1" t="str">
         <f t="shared" si="3"/>
         <v>7670,2938,-7206</v>
       </c>
     </row>
-    <row r="15" spans="3:18">
+    <row r="15" spans="3:19">
       <c r="C15" s="3">
         <v>1010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="7">
+        <v>51</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="6">
         <v>10002</v>
       </c>
-      <c r="F15" s="4">
+      <c r="G15" s="4">
         <v>1</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="1">
+      <c r="H15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="1">
         <v>15819</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>2914</v>
       </c>
-      <c r="L15" s="1">
+      <c r="M15" s="1">
         <v>3879</v>
       </c>
-      <c r="N15" s="1">
+      <c r="O15" s="1">
         <f t="shared" si="0"/>
         <v>15819</v>
       </c>
-      <c r="O15" s="1">
+      <c r="P15" s="1">
         <f t="shared" si="1"/>
         <v>2914</v>
       </c>
-      <c r="P15" s="1">
+      <c r="Q15" s="1">
         <f t="shared" si="2"/>
         <v>3879</v>
       </c>
-      <c r="R15" s="1" t="str">
+      <c r="S15" s="1" t="str">
         <f t="shared" si="3"/>
         <v>15819,2914,3879</v>
       </c>
     </row>
-    <row r="16" spans="3:18">
+    <row r="16" spans="3:19">
       <c r="C16" s="3">
         <v>1011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="4">
+        <v>55</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="4">
         <v>10004</v>
       </c>
-      <c r="F16" s="4">
+      <c r="G16" s="4">
         <v>1</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="1">
+      <c r="H16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K16" s="1">
         <v>25700</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>2800</v>
       </c>
-      <c r="L16" s="1">
+      <c r="M16" s="1">
         <v>-3300</v>
       </c>
-      <c r="N16" s="1">
+      <c r="O16" s="1">
         <f t="shared" si="0"/>
         <v>25700</v>
       </c>
-      <c r="O16" s="1">
+      <c r="P16" s="1">
         <f t="shared" si="1"/>
         <v>2800</v>
       </c>
-      <c r="P16" s="1">
+      <c r="Q16" s="1">
         <f t="shared" si="2"/>
         <v>-3300</v>
       </c>
-      <c r="R16" s="1" t="str">
+      <c r="S16" s="1" t="str">
         <f t="shared" si="3"/>
         <v>25700,2800,-3300</v>
       </c>
     </row>
-    <row r="17" spans="3:18">
+    <row r="17" spans="3:19">
       <c r="C17" s="3">
         <v>1012</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="4">
+        <v>59</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="4">
         <v>10008</v>
       </c>
-      <c r="F17" s="4">
+      <c r="G17" s="4">
         <v>1</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="H17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K17" s="1">
         <v>20300</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>2800</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M17" s="1">
         <v>-4900</v>
       </c>
-      <c r="N17" s="1">
+      <c r="O17" s="1">
         <f t="shared" si="0"/>
         <v>20300</v>
       </c>
-      <c r="O17" s="1">
+      <c r="P17" s="1">
         <f t="shared" si="1"/>
         <v>2800</v>
       </c>
-      <c r="P17" s="1">
+      <c r="Q17" s="1">
         <f t="shared" si="2"/>
         <v>-4900</v>
       </c>
-      <c r="R17" s="1" t="str">
+      <c r="S17" s="1" t="str">
         <f t="shared" si="3"/>
         <v>20300,2800,-4900</v>
       </c>
     </row>
-    <row r="18" spans="3:18">
+    <row r="18" spans="3:19">
       <c r="C18" s="3">
         <v>1013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="4">
+        <v>63</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="4">
         <v>10004</v>
       </c>
-      <c r="F18" s="4">
+      <c r="G18" s="4">
         <v>1</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="1">
+      <c r="H18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="K18" s="1">
         <v>26100</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>2800</v>
       </c>
-      <c r="L18" s="1">
+      <c r="M18" s="1">
         <v>-7300</v>
       </c>
-      <c r="N18" s="1">
+      <c r="O18" s="1">
         <f t="shared" si="0"/>
         <v>26100</v>
       </c>
-      <c r="O18" s="1">
+      <c r="P18" s="1">
         <f t="shared" si="1"/>
         <v>2800</v>
       </c>
-      <c r="P18" s="1">
+      <c r="Q18" s="1">
         <f t="shared" si="2"/>
         <v>-7300</v>
       </c>
-      <c r="R18" s="1" t="str">
+      <c r="S18" s="1" t="str">
         <f t="shared" si="3"/>
         <v>26100,2800,-7300</v>
       </c>
     </row>
-    <row r="19" spans="3:18">
+    <row r="19" spans="3:19">
       <c r="C19" s="3">
         <v>1014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="4">
+        <v>67</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="4">
         <v>10007</v>
       </c>
-      <c r="F19" s="4">
+      <c r="G19" s="4">
         <v>1</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="H19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K19" s="1">
         <v>25310</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>2829</v>
       </c>
-      <c r="L19" s="1">
+      <c r="M19" s="1">
         <v>-4375</v>
       </c>
-      <c r="N19" s="1">
+      <c r="O19" s="1">
         <f t="shared" si="0"/>
         <v>25310</v>
       </c>
-      <c r="O19" s="1">
+      <c r="P19" s="1">
         <f t="shared" si="1"/>
         <v>2829</v>
       </c>
-      <c r="P19" s="1">
+      <c r="Q19" s="1">
         <f t="shared" si="2"/>
         <v>-4375</v>
       </c>
-      <c r="R19" s="1" t="str">
+      <c r="S19" s="1" t="str">
         <f t="shared" si="3"/>
         <v>25310,2829,-4375</v>
       </c>
     </row>
-    <row r="20" spans="3:18">
+    <row r="20" spans="3:19">
       <c r="C20" s="3">
         <v>2001</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="4">
+        <v>71</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="4">
         <v>20001</v>
       </c>
-      <c r="F20" s="4">
+      <c r="G20" s="4">
         <v>15</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H20" s="6"/>
-      <c r="J20" s="1">
+      <c r="H20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="K20" s="1">
         <v>14532</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>2895</v>
       </c>
-      <c r="L20" s="1">
+      <c r="M20" s="1">
         <v>-5271</v>
       </c>
-      <c r="N20" s="1">
+      <c r="O20" s="1">
         <f t="shared" si="0"/>
         <v>14532</v>
       </c>
-      <c r="O20" s="1">
+      <c r="P20" s="1">
         <f t="shared" si="1"/>
         <v>2895</v>
       </c>
-      <c r="P20" s="1">
+      <c r="Q20" s="1">
         <f t="shared" si="2"/>
         <v>-5271</v>
       </c>
-      <c r="R20" s="1" t="str">
+      <c r="S20" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14532,2895,-5271</v>
       </c>
     </row>
-    <row r="21" spans="3:18">
+    <row r="21" spans="3:19">
       <c r="C21" s="3">
         <v>2002</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="4">
+        <v>74</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="4">
         <v>20002</v>
       </c>
-      <c r="F21" s="4">
+      <c r="G21" s="4">
         <v>15</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="J21" s="1">
+      <c r="H21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K21" s="1">
         <v>15259</v>
       </c>
-      <c r="K21" s="1">
+      <c r="L21" s="1">
         <v>2895</v>
       </c>
-      <c r="L21" s="1">
+      <c r="M21" s="1">
         <v>-9335</v>
       </c>
-      <c r="N21" s="1">
+      <c r="O21" s="1">
         <f t="shared" si="0"/>
         <v>15259</v>
       </c>
-      <c r="O21" s="1">
+      <c r="P21" s="1">
         <f t="shared" si="1"/>
         <v>2895</v>
       </c>
-      <c r="P21" s="1">
+      <c r="Q21" s="1">
         <f t="shared" si="2"/>
         <v>-9335</v>
       </c>
-      <c r="R21" s="1" t="str">
+      <c r="S21" s="1" t="str">
         <f t="shared" si="3"/>
         <v>15259,2895,-9335</v>
       </c>
     </row>
-    <row r="22" spans="3:18">
+    <row r="22" spans="3:19">
       <c r="C22" s="3">
         <v>2003</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="4">
+        <v>78</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="4">
         <v>20003</v>
       </c>
-      <c r="F22" s="4">
+      <c r="G22" s="4">
         <v>15</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J22" s="1">
+      <c r="H22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="1">
         <v>15756</v>
       </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
         <v>2895</v>
       </c>
-      <c r="L22" s="1">
+      <c r="M22" s="1">
         <v>-7717</v>
       </c>
-      <c r="N22" s="1">
+      <c r="O22" s="1">
         <f t="shared" si="0"/>
         <v>15756</v>
       </c>
-      <c r="O22" s="1">
+      <c r="P22" s="1">
         <f t="shared" si="1"/>
         <v>2895</v>
       </c>
-      <c r="P22" s="1">
+      <c r="Q22" s="1">
         <f t="shared" si="2"/>
         <v>-7717</v>
       </c>
-      <c r="R22" s="1" t="str">
+      <c r="S22" s="1" t="str">
         <f t="shared" si="3"/>
         <v>15756,2895,-7717</v>
       </c>
     </row>
-    <row r="23" spans="3:18">
+    <row r="23" spans="3:19">
       <c r="C23" s="3">
         <v>2004</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="4">
+        <v>82</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" s="4">
         <v>20004</v>
       </c>
-      <c r="F23" s="4">
+      <c r="G23" s="4">
         <v>15</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J23" s="1">
+      <c r="H23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K23" s="1">
         <v>14613</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>2895</v>
       </c>
-      <c r="L23" s="1">
+      <c r="M23" s="1">
         <v>-7096</v>
       </c>
-      <c r="N23" s="1">
+      <c r="O23" s="1">
         <f t="shared" si="0"/>
         <v>14613</v>
       </c>
-      <c r="O23" s="1">
+      <c r="P23" s="1">
         <f t="shared" si="1"/>
         <v>2895</v>
       </c>
-      <c r="P23" s="1">
+      <c r="Q23" s="1">
         <f t="shared" si="2"/>
         <v>-7096</v>
       </c>
-      <c r="R23" s="1" t="str">
+      <c r="S23" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14613,2895,-7096</v>
       </c>
     </row>
-    <row r="24" spans="3:18">
+    <row r="24" spans="3:19">
       <c r="C24" s="3">
         <v>2005</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="4">
+        <v>86</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="4">
         <v>20005</v>
       </c>
-      <c r="F24" s="4">
+      <c r="G24" s="4">
         <v>15</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="J24" s="1">
+      <c r="H24" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="K24" s="1">
         <v>21779</v>
       </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
         <v>2895</v>
       </c>
-      <c r="L24" s="1">
+      <c r="M24" s="1">
         <v>-2383</v>
       </c>
-      <c r="N24" s="1">
+      <c r="O24" s="1">
         <f t="shared" si="0"/>
         <v>21779</v>
       </c>
-      <c r="O24" s="1">
+      <c r="P24" s="1">
         <f t="shared" si="1"/>
         <v>2895</v>
       </c>
-      <c r="P24" s="1">
+      <c r="Q24" s="1">
         <f t="shared" si="2"/>
         <v>-2383</v>
       </c>
-      <c r="R24" s="1" t="str">
+      <c r="S24" s="1" t="str">
         <f t="shared" si="3"/>
         <v>21779,2895,-2383</v>
       </c>
     </row>
-    <row r="25" spans="3:18">
+    <row r="25" spans="3:19">
       <c r="C25" s="3">
         <v>2011</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="4">
+        <v>90</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="4">
         <v>20001</v>
       </c>
-      <c r="F25" s="4">
+      <c r="G25" s="4">
         <v>15</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="J25" s="1">
+      <c r="H25" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="K25" s="1">
         <v>2139</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <v>2895</v>
       </c>
-      <c r="L25" s="1">
+      <c r="M25" s="1">
         <v>-7394</v>
       </c>
-      <c r="N25" s="1">
+      <c r="O25" s="1">
         <f t="shared" si="0"/>
         <v>2139</v>
       </c>
-      <c r="O25" s="1">
+      <c r="P25" s="1">
         <f t="shared" si="1"/>
         <v>2895</v>
       </c>
-      <c r="P25" s="1">
+      <c r="Q25" s="1">
         <f t="shared" si="2"/>
         <v>-7394</v>
       </c>
-      <c r="R25" s="1" t="str">
+      <c r="S25" s="1" t="str">
         <f t="shared" si="3"/>
         <v>2139,2895,-7394</v>
       </c>
     </row>
-    <row r="26" spans="3:18">
+    <row r="26" spans="3:19">
       <c r="C26" s="3">
         <v>2012</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E26" s="4">
+        <v>94</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="4">
         <v>20002</v>
       </c>
-      <c r="F26" s="4">
+      <c r="G26" s="4">
         <v>15</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="J26" s="1">
+      <c r="H26" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K26" s="1">
         <v>5935</v>
       </c>
-      <c r="K26" s="1">
+      <c r="L26" s="1">
         <v>2895</v>
       </c>
-      <c r="L26" s="1">
+      <c r="M26" s="1">
         <v>-5220</v>
       </c>
-      <c r="N26" s="1">
+      <c r="O26" s="1">
         <f t="shared" si="0"/>
         <v>5935</v>
       </c>
-      <c r="O26" s="1">
+      <c r="P26" s="1">
         <f t="shared" si="1"/>
         <v>2895</v>
       </c>
-      <c r="P26" s="1">
+      <c r="Q26" s="1">
         <f t="shared" si="2"/>
         <v>-5220</v>
       </c>
-      <c r="R26" s="1" t="str">
+      <c r="S26" s="1" t="str">
         <f t="shared" si="3"/>
         <v>5935,2895,-5220</v>
       </c>
     </row>
-    <row r="27" spans="3:18">
+    <row r="27" spans="3:19">
       <c r="C27" s="3">
         <v>2013</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="4">
+        <v>98</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="4">
         <v>20001</v>
       </c>
-      <c r="F27" s="4">
+      <c r="G27" s="4">
         <v>15</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J27" s="1">
+      <c r="H27" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="K27" s="1">
         <v>13404</v>
       </c>
-      <c r="K27" s="1">
+      <c r="L27" s="1">
         <v>2895</v>
       </c>
-      <c r="L27" s="1">
+      <c r="M27" s="1">
         <v>-7275</v>
       </c>
-      <c r="N27" s="1">
+      <c r="O27" s="1">
         <f t="shared" si="0"/>
         <v>13404</v>
       </c>
-      <c r="O27" s="1">
+      <c r="P27" s="1">
         <f t="shared" si="1"/>
         <v>2895</v>
       </c>
-      <c r="P27" s="1">
+      <c r="Q27" s="1">
         <f t="shared" si="2"/>
         <v>-7275</v>
       </c>
-      <c r="R27" s="1" t="str">
+      <c r="S27" s="1" t="str">
         <f t="shared" si="3"/>
         <v>13404,2895,-7275</v>
       </c>
     </row>
-    <row r="28" spans="3:18">
+    <row r="28" spans="3:19">
       <c r="C28" s="3">
         <v>2014</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="4">
+        <v>102</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" s="4">
         <v>20004</v>
       </c>
-      <c r="F28" s="4">
+      <c r="G28" s="4">
         <v>15</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J28" s="1">
+      <c r="H28" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K28" s="1">
         <v>18734</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <v>2814</v>
       </c>
-      <c r="L28" s="1">
+      <c r="M28" s="1">
         <v>3021</v>
       </c>
-      <c r="N28" s="1">
+      <c r="O28" s="1">
         <f t="shared" si="0"/>
         <v>18734</v>
       </c>
-      <c r="O28" s="1">
+      <c r="P28" s="1">
         <f t="shared" si="1"/>
         <v>2814</v>
       </c>
-      <c r="P28" s="1">
+      <c r="Q28" s="1">
         <f t="shared" si="2"/>
         <v>3021</v>
       </c>
-      <c r="R28" s="1" t="str">
+      <c r="S28" s="1" t="str">
         <f t="shared" si="3"/>
         <v>18734,2814,3021</v>
       </c>
     </row>
-    <row r="29" spans="3:18">
+    <row r="29" spans="3:19">
       <c r="C29" s="3">
         <v>3001</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E29" s="4">
+        <v>106</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F29" s="4">
         <v>30001</v>
       </c>
-      <c r="F29" s="4">
+      <c r="G29" s="4">
         <v>15</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H29" s="6"/>
-      <c r="J29" s="1">
+      <c r="H29" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="K29" s="1">
         <v>15369</v>
       </c>
-      <c r="K29" s="1">
+      <c r="L29" s="1">
         <v>2829</v>
       </c>
-      <c r="L29" s="1">
+      <c r="M29" s="1">
         <v>-4216</v>
       </c>
-      <c r="N29" s="1">
+      <c r="O29" s="1">
         <f t="shared" si="0"/>
         <v>15369</v>
       </c>
-      <c r="O29" s="1">
+      <c r="P29" s="1">
         <f t="shared" si="1"/>
         <v>2829</v>
       </c>
-      <c r="P29" s="1">
+      <c r="Q29" s="1">
         <f t="shared" si="2"/>
         <v>-4216</v>
       </c>
-      <c r="R29" s="1" t="str">
+      <c r="S29" s="1" t="str">
         <f t="shared" si="3"/>
         <v>15369,2829,-4216</v>
       </c>
     </row>
-    <row r="30" spans="3:18">
+    <row r="30" spans="3:19">
       <c r="C30" s="3">
         <v>3002</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E30" s="4">
+        <v>109</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" s="4">
         <v>30002</v>
       </c>
-      <c r="F30" s="4">
+      <c r="G30" s="4">
         <v>15</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="J30" s="1">
+      <c r="H30" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K30" s="1">
         <v>13898</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <v>2905</v>
       </c>
-      <c r="L30" s="1">
+      <c r="M30" s="1">
         <v>-4124</v>
       </c>
-      <c r="N30" s="1">
+      <c r="O30" s="1">
         <f t="shared" si="0"/>
         <v>13898</v>
       </c>
-      <c r="O30" s="1">
+      <c r="P30" s="1">
         <f t="shared" si="1"/>
         <v>2905</v>
       </c>
-      <c r="P30" s="1">
+      <c r="Q30" s="1">
         <f t="shared" si="2"/>
         <v>-4124</v>
       </c>
-      <c r="R30" s="1" t="str">
+      <c r="S30" s="1" t="str">
         <f t="shared" si="3"/>
         <v>13898,2905,-4124</v>
       </c>
     </row>
-    <row r="31" spans="3:18">
+    <row r="31" spans="3:19">
       <c r="C31" s="3">
         <v>3003</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E31" s="4">
+        <v>113</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="4">
         <v>30003</v>
       </c>
-      <c r="F31" s="4">
+      <c r="G31" s="4">
         <v>15</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J31" s="1">
+      <c r="H31" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="K31" s="1">
         <v>14983</v>
       </c>
-      <c r="K31" s="1">
+      <c r="L31" s="1">
         <v>2910</v>
       </c>
-      <c r="L31" s="1">
+      <c r="M31" s="1">
         <v>-5997</v>
       </c>
-      <c r="N31" s="1">
+      <c r="O31" s="1">
         <f t="shared" si="0"/>
         <v>14983</v>
       </c>
-      <c r="O31" s="1">
+      <c r="P31" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P31" s="1">
+      <c r="Q31" s="1">
         <f t="shared" si="2"/>
         <v>-5997</v>
       </c>
-      <c r="R31" s="1" t="str">
+      <c r="S31" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14983,2910,-5997</v>
       </c>
     </row>
-    <row r="32" spans="3:18">
+    <row r="32" spans="3:19">
       <c r="C32" s="3">
         <v>3004</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="4">
+        <v>117</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F32" s="4">
         <v>30004</v>
       </c>
-      <c r="F32" s="4">
+      <c r="G32" s="4">
         <v>15</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="H32" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="K32" s="1">
         <v>14000</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <v>2905</v>
       </c>
-      <c r="L32" s="1">
+      <c r="M32" s="1">
         <v>-4277</v>
       </c>
-      <c r="N32" s="1">
+      <c r="O32" s="1">
         <f t="shared" si="0"/>
         <v>14000</v>
       </c>
-      <c r="O32" s="1">
+      <c r="P32" s="1">
         <f t="shared" si="1"/>
         <v>2905</v>
       </c>
-      <c r="P32" s="1">
+      <c r="Q32" s="1">
         <f t="shared" si="2"/>
         <v>-4277</v>
       </c>
-      <c r="R32" s="1" t="str">
+      <c r="S32" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14000,2905,-4277</v>
       </c>
     </row>
-    <row r="33" spans="3:18">
+    <row r="33" spans="3:19">
       <c r="C33" s="3">
         <v>3005</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E33" s="4">
+        <v>121</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="4">
         <v>30005</v>
       </c>
-      <c r="F33" s="4">
+      <c r="G33" s="4">
         <v>15</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="H33" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="K33" s="1">
         <v>14372</v>
       </c>
-      <c r="K33" s="1">
+      <c r="L33" s="1">
         <v>2829</v>
       </c>
-      <c r="L33" s="1">
+      <c r="M33" s="1">
         <v>-7262</v>
       </c>
-      <c r="N33" s="1">
+      <c r="O33" s="1">
         <f t="shared" si="0"/>
         <v>14372</v>
       </c>
-      <c r="O33" s="1">
+      <c r="P33" s="1">
         <f t="shared" si="1"/>
         <v>2829</v>
       </c>
-      <c r="P33" s="1">
+      <c r="Q33" s="1">
         <f t="shared" si="2"/>
         <v>-7262</v>
       </c>
-      <c r="R33" s="1" t="str">
+      <c r="S33" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14372,2829,-7262</v>
       </c>
     </row>
-    <row r="34" spans="3:18">
+    <row r="34" spans="3:19">
       <c r="C34" s="3">
         <v>3006</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" s="4">
+        <v>125</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" s="4">
         <v>30006</v>
       </c>
-      <c r="F34" s="4">
+      <c r="G34" s="4">
         <v>15</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="J34" s="1">
+      <c r="H34" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="K34" s="1">
         <v>14883</v>
       </c>
-      <c r="K34" s="1">
+      <c r="L34" s="1">
         <v>3213</v>
       </c>
-      <c r="L34" s="1">
+      <c r="M34" s="1">
         <v>-7290</v>
       </c>
-      <c r="N34" s="1">
+      <c r="O34" s="1">
         <f t="shared" si="0"/>
         <v>14883</v>
       </c>
-      <c r="O34" s="1">
+      <c r="P34" s="1">
         <f t="shared" si="1"/>
         <v>3213</v>
       </c>
-      <c r="P34" s="1">
+      <c r="Q34" s="1">
         <f t="shared" si="2"/>
         <v>-7290</v>
       </c>
-      <c r="R34" s="1" t="str">
+      <c r="S34" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14883,3213,-7290</v>
       </c>
     </row>
-    <row r="35" spans="3:18">
+    <row r="35" spans="3:19">
       <c r="C35" s="3">
         <v>3011</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E35" s="4">
+        <v>129</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F35" s="4">
         <v>30001</v>
       </c>
-      <c r="F35" s="4">
+      <c r="G35" s="4">
         <v>15</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="J35" s="1">
+      <c r="H35" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="K35" s="1">
         <v>21591</v>
       </c>
-      <c r="K35" s="1">
+      <c r="L35" s="1">
         <v>2829</v>
       </c>
-      <c r="L35" s="1">
+      <c r="M35" s="1">
         <v>-5370</v>
       </c>
-      <c r="N35" s="1">
+      <c r="O35" s="1">
         <f t="shared" si="0"/>
         <v>21591</v>
       </c>
-      <c r="O35" s="1">
+      <c r="P35" s="1">
         <f t="shared" si="1"/>
         <v>2829</v>
       </c>
-      <c r="P35" s="1">
+      <c r="Q35" s="1">
         <f t="shared" si="2"/>
         <v>-5370</v>
       </c>
-      <c r="R35" s="1" t="str">
+      <c r="S35" s="1" t="str">
         <f t="shared" si="3"/>
         <v>21591,2829,-5370</v>
       </c>
     </row>
-    <row r="36" spans="3:18">
+    <row r="36" spans="3:19">
       <c r="C36" s="3">
         <v>3012</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E36" s="4">
+        <v>133</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="4">
         <v>30002</v>
       </c>
-      <c r="F36" s="4">
+      <c r="G36" s="4">
         <v>15</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="J36" s="1">
+      <c r="H36" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="K36" s="1">
         <v>23656</v>
       </c>
-      <c r="K36" s="1">
+      <c r="L36" s="1">
         <v>2905</v>
       </c>
-      <c r="L36" s="1">
+      <c r="M36" s="1">
         <v>-1746</v>
       </c>
-      <c r="N36" s="1">
+      <c r="O36" s="1">
         <f t="shared" si="0"/>
         <v>23656</v>
       </c>
-      <c r="O36" s="1">
+      <c r="P36" s="1">
         <f t="shared" si="1"/>
         <v>2905</v>
       </c>
-      <c r="P36" s="1">
+      <c r="Q36" s="1">
         <f t="shared" si="2"/>
         <v>-1746</v>
       </c>
-      <c r="R36" s="1" t="str">
+      <c r="S36" s="1" t="str">
         <f t="shared" si="3"/>
         <v>23656,2905,-1746</v>
       </c>
     </row>
-    <row r="37" spans="3:18">
+    <row r="37" spans="3:19">
       <c r="C37" s="3">
         <v>3013</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E37" s="4">
+        <v>137</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F37" s="4">
         <v>30002</v>
       </c>
-      <c r="F37" s="4">
+      <c r="G37" s="4">
         <v>15</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="J37" s="1">
+      <c r="H37" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="K37" s="1">
         <v>24258</v>
       </c>
-      <c r="K37" s="1">
+      <c r="L37" s="1">
         <v>2905</v>
       </c>
-      <c r="L37" s="1">
+      <c r="M37" s="1">
         <v>-1821</v>
       </c>
-      <c r="N37" s="1">
+      <c r="O37" s="1">
         <f t="shared" si="0"/>
         <v>24258</v>
       </c>
-      <c r="O37" s="1">
+      <c r="P37" s="1">
         <f t="shared" si="1"/>
         <v>2905</v>
       </c>
-      <c r="P37" s="1">
+      <c r="Q37" s="1">
         <f t="shared" si="2"/>
         <v>-1821</v>
       </c>
-      <c r="R37" s="1" t="str">
+      <c r="S37" s="1" t="str">
         <f t="shared" si="3"/>
         <v>24258,2905,-1821</v>
       </c>
     </row>
-    <row r="38" spans="3:18">
+    <row r="38" spans="3:19">
       <c r="C38" s="3">
         <v>3014</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E38" s="4">
+        <v>141</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F38" s="4">
         <v>30004</v>
       </c>
-      <c r="F38" s="4">
+      <c r="G38" s="4">
         <v>15</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="J38" s="1">
+      <c r="H38" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="K38" s="1">
         <v>16698</v>
       </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
         <v>2752</v>
       </c>
-      <c r="L38" s="1">
+      <c r="M38" s="1">
         <v>3021</v>
       </c>
-      <c r="N38" s="1">
+      <c r="O38" s="1">
         <f t="shared" si="0"/>
         <v>16698</v>
       </c>
-      <c r="O38" s="1">
+      <c r="P38" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P38" s="1">
+      <c r="Q38" s="1">
         <f t="shared" si="2"/>
         <v>3021</v>
       </c>
-      <c r="R38" s="1" t="str">
+      <c r="S38" s="1" t="str">
         <f t="shared" si="3"/>
         <v>16698,2910,3021</v>
       </c>
     </row>
-    <row r="39" spans="3:18">
+    <row r="39" spans="3:19">
       <c r="C39" s="3">
         <v>3015</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" s="4">
+        <v>145</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="4">
         <v>30005</v>
       </c>
-      <c r="F39" s="4">
+      <c r="G39" s="4">
         <v>15</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="J39" s="1">
+      <c r="H39" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="K39" s="1">
         <v>25092</v>
       </c>
-      <c r="K39" s="1">
+      <c r="L39" s="1">
         <v>2729</v>
       </c>
-      <c r="L39" s="1">
+      <c r="M39" s="1">
         <v>-4487</v>
       </c>
-      <c r="N39" s="1">
+      <c r="O39" s="1">
         <f t="shared" si="0"/>
         <v>25092</v>
       </c>
-      <c r="O39" s="1">
+      <c r="P39" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P39" s="1">
+      <c r="Q39" s="1">
         <f t="shared" si="2"/>
         <v>-4487</v>
       </c>
-      <c r="R39" s="1" t="str">
+      <c r="S39" s="1" t="str">
         <f t="shared" si="3"/>
         <v>25092,2910,-4487</v>
       </c>
     </row>
-    <row r="40" spans="3:8">
+    <row r="40" spans="3:9">
       <c r="C40" s="3">
         <v>3016</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E40" s="4">
+        <v>149</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" s="4">
         <v>30006</v>
       </c>
-      <c r="F40" s="4">
+      <c r="G40" s="4">
         <v>16</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="3:18">
+      <c r="H40" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="3:19">
       <c r="C41" s="3">
         <v>4001</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E41" s="4">
+      <c r="D41" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F41" s="4">
         <v>40001</v>
       </c>
-      <c r="F41" s="4">
+      <c r="G41" s="4">
         <v>15</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="H41" s="6"/>
-      <c r="J41" s="1">
+      <c r="H41" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I41" s="9"/>
+      <c r="K41" s="1">
         <v>18834</v>
       </c>
-      <c r="K41" s="1">
+      <c r="L41" s="1">
         <v>2739</v>
       </c>
-      <c r="L41" s="1">
+      <c r="M41" s="1">
         <v>-4755</v>
       </c>
-      <c r="N41" s="1">
+      <c r="O41" s="1">
         <f t="shared" si="0"/>
         <v>18834</v>
       </c>
-      <c r="O41" s="1">
+      <c r="P41" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P41" s="1">
+      <c r="Q41" s="1">
         <f t="shared" si="2"/>
         <v>-4755</v>
       </c>
-      <c r="R41" s="1" t="str">
+      <c r="S41" s="1" t="str">
         <f t="shared" si="3"/>
         <v>18834,2910,-4755</v>
       </c>
     </row>
-    <row r="42" spans="3:18">
+    <row r="42" spans="3:19">
       <c r="C42" s="3">
         <v>4002</v>
       </c>
-      <c r="D42" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E42" s="4">
+      <c r="D42" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="4">
         <v>40002</v>
       </c>
-      <c r="F42" s="4">
+      <c r="G42" s="4">
         <v>15</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="J42" s="1">
+      <c r="H42" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="K42" s="1">
         <v>17650</v>
       </c>
-      <c r="K42" s="1">
+      <c r="L42" s="1">
         <v>2742</v>
       </c>
-      <c r="L42" s="1">
+      <c r="M42" s="1">
         <v>-7510</v>
       </c>
-      <c r="N42" s="1">
+      <c r="O42" s="1">
         <f t="shared" si="0"/>
         <v>17650</v>
       </c>
-      <c r="O42" s="1">
+      <c r="P42" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P42" s="1">
+      <c r="Q42" s="1">
         <f t="shared" si="2"/>
         <v>-7510</v>
       </c>
-      <c r="R42" s="1" t="str">
+      <c r="S42" s="1" t="str">
         <f t="shared" si="3"/>
         <v>17650,2910,-7510</v>
       </c>
     </row>
-    <row r="43" spans="3:18">
+    <row r="43" spans="3:19">
       <c r="C43" s="3">
         <v>4003</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E43" s="4">
+      <c r="D43" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F43" s="4">
         <v>40003</v>
       </c>
-      <c r="F43" s="4">
+      <c r="G43" s="4">
         <v>15</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="J43" s="1">
+      <c r="H43" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="K43" s="1">
         <v>17670</v>
       </c>
-      <c r="K43" s="1">
+      <c r="L43" s="1">
         <v>2829</v>
       </c>
-      <c r="L43" s="1">
+      <c r="M43" s="1">
         <v>-7520</v>
       </c>
-      <c r="N43" s="1">
+      <c r="O43" s="1">
         <f t="shared" si="0"/>
         <v>17670</v>
       </c>
-      <c r="O43" s="1">
+      <c r="P43" s="1">
         <f t="shared" si="1"/>
         <v>2829</v>
       </c>
-      <c r="P43" s="1">
+      <c r="Q43" s="1">
         <f t="shared" si="2"/>
         <v>-7520</v>
       </c>
-      <c r="R43" s="1" t="str">
+      <c r="S43" s="1" t="str">
         <f t="shared" si="3"/>
         <v>17670,2829,-7520</v>
       </c>
     </row>
-    <row r="44" spans="3:18">
+    <row r="44" spans="3:19">
       <c r="C44" s="3">
         <v>4004</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E44" s="4">
+      <c r="D44" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F44" s="4">
         <v>40004</v>
       </c>
-      <c r="F44" s="4">
+      <c r="G44" s="4">
         <v>15</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="J44" s="1">
+      <c r="H44" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="K44" s="1">
         <v>25645</v>
       </c>
-      <c r="K44" s="1">
+      <c r="L44" s="1">
         <v>2779</v>
       </c>
-      <c r="L44" s="1">
+      <c r="M44" s="1">
         <v>-6362</v>
       </c>
-      <c r="N44" s="1">
+      <c r="O44" s="1">
         <f t="shared" si="0"/>
         <v>25645</v>
       </c>
-      <c r="O44" s="1">
+      <c r="P44" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P44" s="1">
+      <c r="Q44" s="1">
         <f t="shared" si="2"/>
         <v>-6362</v>
       </c>
-      <c r="R44" s="1" t="str">
+      <c r="S44" s="1" t="str">
         <f t="shared" si="3"/>
         <v>25645,2910,-6362</v>
       </c>
     </row>
-    <row r="45" spans="3:18">
+    <row r="45" spans="3:19">
       <c r="C45" s="3">
         <v>4005</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" s="4">
+      <c r="D45" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F45" s="4">
         <v>40005</v>
       </c>
-      <c r="F45" s="4">
+      <c r="G45" s="4">
         <v>15</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H45" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="J45" s="1">
+      <c r="H45" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="K45" s="1">
         <v>14301</v>
       </c>
-      <c r="K45" s="1">
+      <c r="L45" s="1">
         <v>2735</v>
       </c>
-      <c r="L45" s="1">
+      <c r="M45" s="1">
         <v>2212</v>
       </c>
-      <c r="N45" s="1">
+      <c r="O45" s="1">
         <f t="shared" si="0"/>
         <v>14301</v>
       </c>
-      <c r="O45" s="1">
+      <c r="P45" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P45" s="1">
+      <c r="Q45" s="1">
         <f t="shared" si="2"/>
         <v>2212</v>
       </c>
-      <c r="R45" s="1" t="str">
+      <c r="S45" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14301,2910,2212</v>
       </c>
     </row>
-    <row r="46" spans="3:18">
+    <row r="46" spans="3:19">
       <c r="C46" s="3">
         <v>4006</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E46" s="4">
+      <c r="D46" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F46" s="4">
         <v>40006</v>
       </c>
-      <c r="F46" s="4">
+      <c r="G46" s="4">
         <v>15</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="J46" s="1">
+      <c r="H46" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="K46" s="1">
         <v>14611</v>
       </c>
-      <c r="K46" s="1">
+      <c r="L46" s="1">
         <v>2829</v>
       </c>
-      <c r="L46" s="1">
+      <c r="M46" s="1">
         <v>-2951</v>
       </c>
-      <c r="N46" s="1">
+      <c r="O46" s="1">
         <f t="shared" si="0"/>
         <v>14611</v>
       </c>
-      <c r="O46" s="1">
+      <c r="P46" s="1">
         <f t="shared" si="1"/>
         <v>2829</v>
       </c>
-      <c r="P46" s="1">
+      <c r="Q46" s="1">
         <f t="shared" si="2"/>
         <v>-2951</v>
       </c>
-      <c r="R46" s="1" t="str">
+      <c r="S46" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14611,2829,-2951</v>
       </c>
     </row>
-    <row r="47" spans="3:18">
+    <row r="47" spans="3:19">
       <c r="C47" s="3">
         <v>4007</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E47" s="4">
+      <c r="D47" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F47" s="4">
         <v>40007</v>
       </c>
-      <c r="F47" s="4">
+      <c r="G47" s="4">
         <v>15</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="J47" s="1">
+      <c r="H47" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="K47" s="1">
         <v>24409</v>
       </c>
-      <c r="K47" s="1">
+      <c r="L47" s="1">
         <v>2760</v>
       </c>
-      <c r="L47" s="1">
+      <c r="M47" s="1">
         <v>-11440</v>
       </c>
-      <c r="N47" s="1">
+      <c r="O47" s="1">
         <f t="shared" si="0"/>
         <v>24409</v>
       </c>
-      <c r="O47" s="1">
+      <c r="P47" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P47" s="1">
+      <c r="Q47" s="1">
         <f t="shared" si="2"/>
         <v>-11440</v>
       </c>
-      <c r="R47" s="1" t="str">
+      <c r="S47" s="1" t="str">
         <f t="shared" si="3"/>
         <v>24409,2910,-11440</v>
       </c>
     </row>
-    <row r="48" spans="3:18">
+    <row r="48" spans="3:19">
       <c r="C48" s="3">
         <v>4011</v>
       </c>
-      <c r="D48" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E48" s="4">
+      <c r="D48" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F48" s="4">
         <v>40001</v>
       </c>
-      <c r="F48" s="7">
+      <c r="G48" s="6">
         <v>15</v>
       </c>
-      <c r="G48" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="J48" s="1">
+      <c r="H48" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="K48" s="1">
         <v>22343</v>
       </c>
-      <c r="K48" s="1">
+      <c r="L48" s="1">
         <v>2739</v>
       </c>
-      <c r="L48" s="1">
+      <c r="M48" s="1">
         <v>2283</v>
       </c>
-      <c r="N48" s="1">
+      <c r="O48" s="1">
         <f t="shared" si="0"/>
         <v>22343</v>
       </c>
-      <c r="O48" s="1">
+      <c r="P48" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P48" s="1">
+      <c r="Q48" s="1">
         <f t="shared" si="2"/>
         <v>2283</v>
       </c>
-      <c r="R48" s="1" t="str">
+      <c r="S48" s="1" t="str">
         <f t="shared" si="3"/>
         <v>22343,2910,2283</v>
       </c>
     </row>
-    <row r="49" spans="3:18">
+    <row r="49" spans="3:19">
       <c r="C49" s="3">
         <v>4012</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E49" s="4">
+      <c r="D49" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F49" s="4">
         <v>40001</v>
       </c>
-      <c r="F49" s="7">
+      <c r="G49" s="6">
         <v>15</v>
       </c>
-      <c r="G49" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="H49" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="J49" s="1">
+      <c r="H49" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="K49" s="1">
         <v>22823</v>
       </c>
-      <c r="K49" s="1">
+      <c r="L49" s="1">
         <v>2678</v>
       </c>
-      <c r="L49" s="1">
+      <c r="M49" s="1">
         <v>-4349</v>
       </c>
-      <c r="N49" s="1">
+      <c r="O49" s="1">
         <f t="shared" si="0"/>
         <v>22823</v>
       </c>
-      <c r="O49" s="1">
+      <c r="P49" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P49" s="1">
+      <c r="Q49" s="1">
         <f t="shared" si="2"/>
         <v>-4349</v>
       </c>
-      <c r="R49" s="1" t="str">
+      <c r="S49" s="1" t="str">
         <f t="shared" si="3"/>
         <v>22823,2910,-4349</v>
       </c>
     </row>
-    <row r="50" spans="3:18">
+    <row r="50" spans="3:19">
       <c r="C50" s="3">
         <v>4013</v>
       </c>
-      <c r="D50" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E50" s="4">
+      <c r="D50" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F50" s="4">
         <v>40003</v>
       </c>
-      <c r="F50" s="7">
+      <c r="G50" s="6">
         <v>15</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="J50" s="1">
+      <c r="H50" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="K50" s="1">
         <v>15969</v>
       </c>
-      <c r="K50" s="1">
+      <c r="L50" s="1">
         <v>2829</v>
       </c>
-      <c r="L50" s="1">
+      <c r="M50" s="1">
         <v>-1212</v>
       </c>
-      <c r="N50" s="1">
+      <c r="O50" s="1">
         <f t="shared" si="0"/>
         <v>15969</v>
       </c>
-      <c r="O50" s="1">
+      <c r="P50" s="1">
         <f t="shared" si="1"/>
         <v>2829</v>
       </c>
-      <c r="P50" s="1">
+      <c r="Q50" s="1">
         <f t="shared" si="2"/>
         <v>-1212</v>
       </c>
-      <c r="R50" s="1" t="str">
+      <c r="S50" s="1" t="str">
         <f t="shared" si="3"/>
         <v>15969,2829,-1212</v>
       </c>
     </row>
-    <row r="51" spans="3:18">
+    <row r="51" spans="3:19">
       <c r="C51" s="3">
         <v>4014</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E51" s="4">
+      <c r="D51" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F51" s="4">
         <v>40004</v>
       </c>
-      <c r="F51" s="7">
+      <c r="G51" s="6">
         <v>15</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="H51" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="J51" s="1">
+      <c r="H51" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="K51" s="1">
         <v>15161</v>
       </c>
-      <c r="K51" s="1">
+      <c r="L51" s="1">
         <v>2775</v>
       </c>
-      <c r="L51" s="1">
+      <c r="M51" s="1">
         <v>-5520</v>
       </c>
-      <c r="N51" s="1">
+      <c r="O51" s="1">
         <f t="shared" si="0"/>
         <v>15161</v>
       </c>
-      <c r="O51" s="1">
+      <c r="P51" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P51" s="1">
+      <c r="Q51" s="1">
         <f t="shared" si="2"/>
         <v>-5520</v>
       </c>
-      <c r="R51" s="1" t="str">
+      <c r="S51" s="1" t="str">
         <f t="shared" si="3"/>
         <v>15161,2910,-5520</v>
       </c>
     </row>
-    <row r="52" spans="3:18">
+    <row r="52" spans="3:19">
       <c r="C52" s="3">
         <v>4015</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E52" s="4">
+        <v>196</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F52" s="4">
         <v>40006</v>
       </c>
-      <c r="F52" s="7">
+      <c r="G52" s="6">
         <v>15</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H52" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="J52" s="1">
+      <c r="H52" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="K52" s="1">
         <v>28843</v>
       </c>
-      <c r="K52" s="1">
+      <c r="L52" s="1">
         <v>2829</v>
       </c>
-      <c r="L52" s="1">
+      <c r="M52" s="1">
         <v>-6720</v>
       </c>
-      <c r="N52" s="1">
+      <c r="O52" s="1">
         <f t="shared" si="0"/>
         <v>28843</v>
       </c>
-      <c r="O52" s="1">
+      <c r="P52" s="1">
         <f t="shared" si="1"/>
         <v>2829</v>
       </c>
-      <c r="P52" s="1">
+      <c r="Q52" s="1">
         <f t="shared" si="2"/>
         <v>-6720</v>
       </c>
-      <c r="R52" s="1" t="str">
+      <c r="S52" s="1" t="str">
         <f t="shared" si="3"/>
         <v>28843,2829,-6720</v>
       </c>
     </row>
-    <row r="53" spans="3:18">
+    <row r="53" spans="3:19">
       <c r="C53" s="3">
         <v>4016</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E53" s="4">
+      <c r="D53" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="F53" s="4">
         <v>40002</v>
       </c>
-      <c r="F53" s="7">
+      <c r="G53" s="6">
         <v>15</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="J53" s="1">
+      <c r="H53" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="K53" s="1">
         <v>20397</v>
       </c>
-      <c r="K53" s="1">
+      <c r="L53" s="1">
         <v>2742</v>
       </c>
-      <c r="L53" s="1">
+      <c r="M53" s="1">
         <v>3676</v>
       </c>
-      <c r="N53" s="1">
+      <c r="O53" s="1">
         <f t="shared" si="0"/>
         <v>20397</v>
       </c>
-      <c r="O53" s="1">
+      <c r="P53" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P53" s="1">
+      <c r="Q53" s="1">
         <f t="shared" si="2"/>
         <v>3676</v>
       </c>
-      <c r="R53" s="1" t="str">
+      <c r="S53" s="1" t="str">
         <f t="shared" si="3"/>
         <v>20397,2910,3676</v>
       </c>
     </row>
-    <row r="54" spans="3:18">
+    <row r="54" spans="3:19">
       <c r="C54" s="3">
         <v>5001</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E54" s="4">
+        <v>204</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F54" s="4">
         <v>50001</v>
       </c>
-      <c r="F54" s="7">
+      <c r="G54" s="6">
         <v>15</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="J54" s="1">
+      <c r="H54" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="K54" s="1">
         <v>231</v>
       </c>
-      <c r="K54" s="1">
+      <c r="L54" s="1">
         <v>2731</v>
       </c>
-      <c r="L54" s="1">
+      <c r="M54" s="1">
         <v>-1310</v>
       </c>
-      <c r="N54" s="1">
+      <c r="O54" s="1">
         <f t="shared" si="0"/>
         <v>231</v>
       </c>
-      <c r="O54" s="1">
+      <c r="P54" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P54" s="1">
+      <c r="Q54" s="1">
         <f t="shared" si="2"/>
         <v>-1310</v>
       </c>
-      <c r="R54" s="1" t="str">
+      <c r="S54" s="1" t="str">
         <f t="shared" si="3"/>
         <v>231,2910,-1310</v>
       </c>
     </row>
-    <row r="55" spans="3:18">
+    <row r="55" spans="3:19">
       <c r="C55" s="3">
         <v>5002</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E55" s="4">
+        <v>207</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F55" s="4">
         <v>50002</v>
       </c>
-      <c r="F55" s="7">
+      <c r="G55" s="6">
         <v>15</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="J55" s="1">
+      <c r="H55" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="K55" s="1">
         <v>15993</v>
       </c>
-      <c r="K55" s="1">
+      <c r="L55" s="1">
         <v>2773</v>
       </c>
-      <c r="L55" s="1">
+      <c r="M55" s="1">
         <v>-7254</v>
       </c>
-      <c r="N55" s="1">
+      <c r="O55" s="1">
         <f t="shared" si="0"/>
         <v>15993</v>
       </c>
-      <c r="O55" s="1">
+      <c r="P55" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P55" s="1">
+      <c r="Q55" s="1">
         <f t="shared" si="2"/>
         <v>-7254</v>
       </c>
-      <c r="R55" s="1" t="str">
+      <c r="S55" s="1" t="str">
         <f t="shared" si="3"/>
         <v>15993,2910,-7254</v>
       </c>
     </row>
-    <row r="56" spans="3:18">
+    <row r="56" spans="3:19">
       <c r="C56" s="3">
         <v>5003</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E56" s="4">
+        <v>211</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F56" s="4">
         <v>50003</v>
       </c>
-      <c r="F56" s="7">
+      <c r="G56" s="6">
         <v>15</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="H56" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="J56" s="1">
+      <c r="H56" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="K56" s="1">
         <v>15110</v>
       </c>
-      <c r="K56" s="1">
+      <c r="L56" s="1">
         <v>2759</v>
       </c>
-      <c r="L56" s="1">
+      <c r="M56" s="1">
         <v>10008</v>
       </c>
-      <c r="N56" s="1">
+      <c r="O56" s="1">
         <f t="shared" si="0"/>
         <v>15110</v>
       </c>
-      <c r="O56" s="1">
+      <c r="P56" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P56" s="1">
+      <c r="Q56" s="1">
         <f t="shared" si="2"/>
         <v>10008</v>
       </c>
-      <c r="R56" s="1" t="str">
+      <c r="S56" s="1" t="str">
         <f t="shared" si="3"/>
         <v>15110,2910,10008</v>
       </c>
     </row>
-    <row r="57" spans="3:18">
+    <row r="57" spans="3:19">
       <c r="C57" s="3">
         <v>5004</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E57" s="4">
+        <v>215</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F57" s="4">
         <v>50004</v>
       </c>
-      <c r="F57" s="7">
+      <c r="G57" s="6">
         <v>15</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="J57" s="1">
+      <c r="H57" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="K57" s="1">
         <v>14457</v>
       </c>
-      <c r="K57" s="1">
+      <c r="L57" s="1">
         <v>2647</v>
       </c>
-      <c r="L57" s="1">
+      <c r="M57" s="1">
         <v>-7165</v>
       </c>
-      <c r="N57" s="1">
+      <c r="O57" s="1">
         <f t="shared" si="0"/>
         <v>14457</v>
       </c>
-      <c r="O57" s="1">
+      <c r="P57" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P57" s="1">
+      <c r="Q57" s="1">
         <f t="shared" si="2"/>
         <v>-7165</v>
       </c>
-      <c r="R57" s="1" t="str">
+      <c r="S57" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14457,2910,-7165</v>
       </c>
     </row>
-    <row r="58" spans="3:18">
+    <row r="58" spans="3:19">
       <c r="C58" s="3">
         <v>5005</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E58" s="4">
+        <v>219</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F58" s="4">
         <v>50005</v>
       </c>
-      <c r="F58" s="7">
+      <c r="G58" s="6">
         <v>15</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="H58" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="J58" s="1">
+      <c r="H58" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="K58" s="1">
         <v>3289</v>
       </c>
-      <c r="K58" s="1">
+      <c r="L58" s="1">
         <v>2814</v>
       </c>
-      <c r="L58" s="1">
+      <c r="M58" s="1">
         <v>22929</v>
       </c>
-      <c r="N58" s="1">
+      <c r="O58" s="1">
         <f t="shared" si="0"/>
         <v>3289</v>
       </c>
-      <c r="O58" s="1">
+      <c r="P58" s="1">
         <f t="shared" si="1"/>
         <v>2814</v>
       </c>
-      <c r="P58" s="1">
+      <c r="Q58" s="1">
         <f t="shared" si="2"/>
         <v>22929</v>
       </c>
-      <c r="R58" s="1" t="str">
+      <c r="S58" s="1" t="str">
         <f t="shared" si="3"/>
         <v>3289,2814,22929</v>
       </c>
     </row>
-    <row r="59" spans="3:18">
+    <row r="59" spans="3:19">
       <c r="C59" s="3">
         <v>5006</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E59" s="4">
+        <v>223</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F59" s="4">
         <v>50006</v>
       </c>
-      <c r="F59" s="7">
+      <c r="G59" s="6">
         <v>15</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="J59" s="1">
+      <c r="H59" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="K59" s="1">
         <v>38905</v>
       </c>
-      <c r="K59" s="1">
+      <c r="L59" s="1">
         <v>2317</v>
       </c>
-      <c r="L59" s="1">
+      <c r="M59" s="1">
         <v>14113</v>
       </c>
-      <c r="N59" s="1">
+      <c r="O59" s="1">
         <f t="shared" si="0"/>
         <v>38905</v>
       </c>
-      <c r="O59" s="1">
+      <c r="P59" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P59" s="1">
+      <c r="Q59" s="1">
         <f t="shared" si="2"/>
         <v>14113</v>
       </c>
-      <c r="R59" s="1" t="str">
+      <c r="S59" s="1" t="str">
         <f t="shared" si="3"/>
         <v>38905,2910,14113</v>
       </c>
     </row>
-    <row r="60" spans="3:18">
+    <row r="60" spans="3:19">
       <c r="C60" s="3">
         <v>5007</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E60" s="4">
+        <v>227</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F60" s="4">
         <v>50007</v>
       </c>
-      <c r="F60" s="7">
+      <c r="G60" s="6">
         <v>15</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="J60" s="1">
+      <c r="H60" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="K60" s="1">
         <v>38443</v>
       </c>
-      <c r="K60" s="1">
+      <c r="L60" s="1">
         <v>2388</v>
       </c>
-      <c r="L60" s="1">
+      <c r="M60" s="1">
         <v>13759</v>
       </c>
-      <c r="N60" s="1">
+      <c r="O60" s="1">
         <f t="shared" si="0"/>
         <v>38443</v>
       </c>
-      <c r="O60" s="1">
+      <c r="P60" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P60" s="1">
+      <c r="Q60" s="1">
         <f t="shared" si="2"/>
         <v>13759</v>
       </c>
-      <c r="R60" s="1" t="str">
+      <c r="S60" s="1" t="str">
         <f t="shared" si="3"/>
         <v>38443,2910,13759</v>
       </c>
     </row>
-    <row r="61" spans="3:18">
+    <row r="61" spans="3:19">
       <c r="C61" s="3">
         <v>5011</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E61" s="4">
+        <v>231</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F61" s="4">
         <v>50001</v>
       </c>
-      <c r="F61" s="7">
+      <c r="G61" s="6">
         <v>15</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="J61" s="1">
+      <c r="H61" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="K61" s="1">
         <v>7832</v>
       </c>
-      <c r="K61" s="1">
+      <c r="L61" s="1">
         <v>2704</v>
       </c>
-      <c r="L61" s="1">
+      <c r="M61" s="1">
         <v>-6881</v>
       </c>
-      <c r="N61" s="1">
+      <c r="O61" s="1">
         <f t="shared" si="0"/>
         <v>7832</v>
       </c>
-      <c r="O61" s="1">
+      <c r="P61" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P61" s="1">
+      <c r="Q61" s="1">
         <f t="shared" si="2"/>
         <v>-6881</v>
       </c>
-      <c r="R61" s="1" t="str">
+      <c r="S61" s="1" t="str">
         <f t="shared" si="3"/>
         <v>7832,2910,-6881</v>
       </c>
     </row>
-    <row r="62" spans="3:18">
+    <row r="62" spans="3:19">
       <c r="C62" s="3">
         <v>5012</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E62" s="4">
+        <v>235</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F62" s="4">
         <v>50002</v>
       </c>
-      <c r="F62" s="7">
+      <c r="G62" s="6">
         <v>15</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="H62" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="J62" s="1">
+      <c r="H62" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K62" s="1">
         <v>13618</v>
       </c>
-      <c r="K62" s="1">
+      <c r="L62" s="1">
         <v>2732</v>
       </c>
-      <c r="L62" s="1">
+      <c r="M62" s="1">
         <v>6375</v>
       </c>
-      <c r="N62" s="1">
+      <c r="O62" s="1">
         <f t="shared" si="0"/>
         <v>13618</v>
       </c>
-      <c r="O62" s="1">
+      <c r="P62" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P62" s="1">
+      <c r="Q62" s="1">
         <f t="shared" si="2"/>
         <v>6375</v>
       </c>
-      <c r="R62" s="1" t="str">
+      <c r="S62" s="1" t="str">
         <f t="shared" si="3"/>
         <v>13618,2910,6375</v>
       </c>
     </row>
-    <row r="63" spans="3:18">
+    <row r="63" spans="3:19">
       <c r="C63" s="3">
         <v>5013</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E63" s="4">
+        <v>239</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F63" s="4">
         <v>50003</v>
       </c>
-      <c r="F63" s="7">
+      <c r="G63" s="6">
         <v>15</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H63" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="J63" s="1">
+      <c r="H63" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="K63" s="1">
         <v>14432</v>
       </c>
-      <c r="K63" s="1">
+      <c r="L63" s="1">
         <v>2791</v>
       </c>
-      <c r="L63" s="1">
+      <c r="M63" s="1">
         <v>-6764</v>
       </c>
-      <c r="N63" s="1">
+      <c r="O63" s="1">
         <f t="shared" si="0"/>
         <v>14432</v>
       </c>
-      <c r="O63" s="1">
+      <c r="P63" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P63" s="1">
+      <c r="Q63" s="1">
         <f t="shared" si="2"/>
         <v>-6764</v>
       </c>
-      <c r="R63" s="1" t="str">
+      <c r="S63" s="1" t="str">
         <f t="shared" si="3"/>
         <v>14432,2910,-6764</v>
       </c>
     </row>
-    <row r="64" spans="3:18">
+    <row r="64" spans="3:19">
       <c r="C64" s="3">
         <v>5014</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E64" s="4">
+        <v>243</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F64" s="4">
         <v>50004</v>
       </c>
-      <c r="F64" s="7">
+      <c r="G64" s="6">
         <v>15</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="H64" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="J64" s="1">
+      <c r="H64" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I64" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="K64" s="1">
         <v>38484</v>
       </c>
-      <c r="K64" s="1">
+      <c r="L64" s="1">
         <v>2319</v>
       </c>
-      <c r="L64" s="1">
+      <c r="M64" s="1">
         <v>13914</v>
       </c>
-      <c r="N64" s="1">
+      <c r="O64" s="1">
         <f t="shared" si="0"/>
         <v>38484</v>
       </c>
-      <c r="O64" s="1">
+      <c r="P64" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P64" s="1">
+      <c r="Q64" s="1">
         <f t="shared" si="2"/>
         <v>13914</v>
       </c>
-      <c r="R64" s="1" t="str">
+      <c r="S64" s="1" t="str">
         <f t="shared" si="3"/>
         <v>38484,2910,13914</v>
       </c>
     </row>
-    <row r="65" spans="3:18">
+    <row r="65" spans="3:19">
       <c r="C65" s="3">
         <v>5015</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E65" s="4">
+        <v>247</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F65" s="4">
         <v>50005</v>
       </c>
-      <c r="F65" s="7">
+      <c r="G65" s="6">
         <v>15</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="H65" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="J65" s="1">
+      <c r="H65" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="K65" s="1">
         <v>-5260</v>
       </c>
-      <c r="K65" s="1">
+      <c r="L65" s="1">
         <v>2563</v>
       </c>
-      <c r="L65" s="1">
+      <c r="M65" s="1">
         <v>-7262</v>
       </c>
-      <c r="N65" s="1">
+      <c r="O65" s="1">
         <f t="shared" si="0"/>
         <v>-5260</v>
       </c>
-      <c r="O65" s="1">
+      <c r="P65" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P65" s="1">
+      <c r="Q65" s="1">
         <f t="shared" si="2"/>
         <v>-7262</v>
       </c>
-      <c r="R65" s="1" t="str">
+      <c r="S65" s="1" t="str">
         <f t="shared" si="3"/>
         <v>-5260,2910,-7262</v>
       </c>
     </row>
-    <row r="66" spans="3:18">
+    <row r="66" spans="3:19">
       <c r="C66" s="3">
         <v>5016</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E66" s="4">
+        <v>251</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F66" s="4">
         <v>50006</v>
       </c>
-      <c r="F66" s="4">
+      <c r="G66" s="4">
         <v>15</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="H66" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="J66" s="1">
+      <c r="H66" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="K66" s="1">
         <v>6724</v>
       </c>
-      <c r="K66" s="1">
+      <c r="L66" s="1">
         <v>2214</v>
       </c>
-      <c r="L66" s="1">
+      <c r="M66" s="1">
         <v>-8579</v>
       </c>
-      <c r="N66" s="1">
+      <c r="O66" s="1">
         <f t="shared" si="0"/>
         <v>6724</v>
       </c>
-      <c r="O66" s="1">
+      <c r="P66" s="1">
         <f t="shared" si="1"/>
         <v>2910</v>
       </c>
-      <c r="P66" s="1">
+      <c r="Q66" s="1">
         <f t="shared" si="2"/>
         <v>-8579</v>
       </c>
-      <c r="R66" s="1" t="str">
+      <c r="S66" s="1" t="str">
         <f t="shared" si="3"/>
         <v>6724,2910,-8579</v>
       </c>

--- a/Excel/DungeonTransferConfig.xlsx
+++ b/Excel/DungeonTransferConfig.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="256">
+  <si>
+    <t>c</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
@@ -1878,7 +1881,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:S66"/>
+  <dimension ref="C2:S66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -1891,73 +1894,78 @@
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="5:5">
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="3" spans="3:9">
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="3:9">
       <c r="C4" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="3:9">
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="3:9">
@@ -1965,10 +1973,10 @@
         <v>1001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="4">
         <v>10001</v>
@@ -1977,10 +1985,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="3:19">
@@ -1988,10 +1996,10 @@
         <v>1002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="6">
         <v>10002</v>
@@ -2000,10 +2008,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7" s="1">
         <v>15200</v>
@@ -2036,10 +2044,10 @@
         <v>1003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="4">
         <v>10003</v>
@@ -2048,10 +2056,10 @@
         <v>5</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K8" s="1">
         <v>16292</v>
@@ -2084,10 +2092,10 @@
         <v>1004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="4">
         <v>10004</v>
@@ -2096,10 +2104,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K9" s="1">
         <v>15400</v>
@@ -2132,10 +2140,10 @@
         <v>1005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="4">
         <v>10005</v>
@@ -2144,10 +2152,10 @@
         <v>5</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K10" s="1">
         <v>14400</v>
@@ -2180,10 +2188,10 @@
         <v>1006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F11" s="4">
         <v>10006</v>
@@ -2192,10 +2200,10 @@
         <v>12</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K11" s="1">
         <v>16800</v>
@@ -2228,10 +2236,10 @@
         <v>1007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F12" s="4">
         <v>10007</v>
@@ -2240,10 +2248,10 @@
         <v>8</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K12" s="1">
         <v>14300</v>
@@ -2276,10 +2284,10 @@
         <v>1008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F13" s="4">
         <v>10008</v>
@@ -2288,10 +2296,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K13" s="1">
         <v>14400</v>
@@ -2324,10 +2332,10 @@
         <v>1009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14" s="4">
         <v>10001</v>
@@ -2336,10 +2344,10 @@
         <v>1</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K14" s="1">
         <v>7670</v>
@@ -2372,10 +2380,10 @@
         <v>1010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F15" s="6">
         <v>10002</v>
@@ -2384,10 +2392,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K15" s="1">
         <v>15819</v>
@@ -2420,10 +2428,10 @@
         <v>1011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F16" s="4">
         <v>10004</v>
@@ -2432,10 +2440,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K16" s="1">
         <v>25700</v>
@@ -2468,10 +2476,10 @@
         <v>1012</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F17" s="4">
         <v>10008</v>
@@ -2480,10 +2488,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K17" s="1">
         <v>20300</v>
@@ -2516,10 +2524,10 @@
         <v>1013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" s="4">
         <v>10004</v>
@@ -2528,10 +2536,10 @@
         <v>1</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K18" s="1">
         <v>26100</v>
@@ -2564,10 +2572,10 @@
         <v>1014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" s="4">
         <v>10007</v>
@@ -2576,10 +2584,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K19" s="1">
         <v>25310</v>
@@ -2612,10 +2620,10 @@
         <v>2001</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F20" s="4">
         <v>20001</v>
@@ -2624,7 +2632,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I20" s="9"/>
       <c r="K20" s="1">
@@ -2658,10 +2666,10 @@
         <v>2002</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F21" s="4">
         <v>20002</v>
@@ -2670,10 +2678,10 @@
         <v>15</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K21" s="1">
         <v>15259</v>
@@ -2706,10 +2714,10 @@
         <v>2003</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="4">
         <v>20003</v>
@@ -2718,10 +2726,10 @@
         <v>15</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K22" s="1">
         <v>15756</v>
@@ -2754,10 +2762,10 @@
         <v>2004</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F23" s="4">
         <v>20004</v>
@@ -2766,10 +2774,10 @@
         <v>15</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K23" s="1">
         <v>14613</v>
@@ -2802,10 +2810,10 @@
         <v>2005</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F24" s="4">
         <v>20005</v>
@@ -2814,10 +2822,10 @@
         <v>15</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K24" s="1">
         <v>21779</v>
@@ -2850,10 +2858,10 @@
         <v>2011</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F25" s="4">
         <v>20001</v>
@@ -2862,10 +2870,10 @@
         <v>15</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" s="1">
         <v>2139</v>
@@ -2898,10 +2906,10 @@
         <v>2012</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F26" s="4">
         <v>20002</v>
@@ -2910,10 +2918,10 @@
         <v>15</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K26" s="1">
         <v>5935</v>
@@ -2946,10 +2954,10 @@
         <v>2013</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F27" s="4">
         <v>20001</v>
@@ -2958,10 +2966,10 @@
         <v>15</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K27" s="1">
         <v>13404</v>
@@ -2994,10 +3002,10 @@
         <v>2014</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F28" s="4">
         <v>20004</v>
@@ -3006,10 +3014,10 @@
         <v>15</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K28" s="1">
         <v>18734</v>
@@ -3042,10 +3050,10 @@
         <v>3001</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" s="4">
         <v>30001</v>
@@ -3054,7 +3062,7 @@
         <v>15</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I29" s="9"/>
       <c r="K29" s="1">
@@ -3088,10 +3096,10 @@
         <v>3002</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F30" s="4">
         <v>30002</v>
@@ -3100,10 +3108,10 @@
         <v>15</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K30" s="1">
         <v>13898</v>
@@ -3136,10 +3144,10 @@
         <v>3003</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F31" s="4">
         <v>30003</v>
@@ -3148,10 +3156,10 @@
         <v>15</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K31" s="1">
         <v>14983</v>
@@ -3184,10 +3192,10 @@
         <v>3004</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="4">
         <v>30004</v>
@@ -3196,10 +3204,10 @@
         <v>15</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K32" s="1">
         <v>14000</v>
@@ -3232,10 +3240,10 @@
         <v>3005</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F33" s="4">
         <v>30005</v>
@@ -3244,10 +3252,10 @@
         <v>15</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K33" s="1">
         <v>14372</v>
@@ -3280,10 +3288,10 @@
         <v>3006</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F34" s="4">
         <v>30006</v>
@@ -3292,10 +3300,10 @@
         <v>15</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K34" s="1">
         <v>14883</v>
@@ -3328,10 +3336,10 @@
         <v>3011</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F35" s="4">
         <v>30001</v>
@@ -3340,10 +3348,10 @@
         <v>15</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K35" s="1">
         <v>21591</v>
@@ -3376,10 +3384,10 @@
         <v>3012</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="4">
         <v>30002</v>
@@ -3388,10 +3396,10 @@
         <v>15</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K36" s="1">
         <v>23656</v>
@@ -3424,10 +3432,10 @@
         <v>3013</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F37" s="4">
         <v>30002</v>
@@ -3436,10 +3444,10 @@
         <v>15</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K37" s="1">
         <v>24258</v>
@@ -3472,10 +3480,10 @@
         <v>3014</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="4">
         <v>30004</v>
@@ -3484,10 +3492,10 @@
         <v>15</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K38" s="1">
         <v>16698</v>
@@ -3520,10 +3528,10 @@
         <v>3015</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="4">
         <v>30005</v>
@@ -3532,10 +3540,10 @@
         <v>15</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K39" s="1">
         <v>25092</v>
@@ -3568,10 +3576,10 @@
         <v>3016</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F40" s="4">
         <v>30006</v>
@@ -3580,10 +3588,10 @@
         <v>16</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="3:19">
@@ -3591,10 +3599,10 @@
         <v>4001</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="4">
         <v>40001</v>
@@ -3603,7 +3611,7 @@
         <v>15</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I41" s="9"/>
       <c r="K41" s="1">
@@ -3637,10 +3645,10 @@
         <v>4002</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="4">
         <v>40002</v>
@@ -3649,10 +3657,10 @@
         <v>15</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K42" s="1">
         <v>17650</v>
@@ -3685,10 +3693,10 @@
         <v>4003</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F43" s="4">
         <v>40003</v>
@@ -3697,10 +3705,10 @@
         <v>15</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K43" s="1">
         <v>17670</v>
@@ -3733,10 +3741,10 @@
         <v>4004</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F44" s="4">
         <v>40004</v>
@@ -3745,10 +3753,10 @@
         <v>15</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K44" s="1">
         <v>25645</v>
@@ -3781,10 +3789,10 @@
         <v>4005</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F45" s="4">
         <v>40005</v>
@@ -3793,10 +3801,10 @@
         <v>15</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K45" s="1">
         <v>14301</v>
@@ -3829,10 +3837,10 @@
         <v>4006</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F46" s="4">
         <v>40006</v>
@@ -3841,10 +3849,10 @@
         <v>15</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K46" s="1">
         <v>14611</v>
@@ -3877,10 +3885,10 @@
         <v>4007</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F47" s="4">
         <v>40007</v>
@@ -3889,10 +3897,10 @@
         <v>15</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K47" s="1">
         <v>24409</v>
@@ -3925,10 +3933,10 @@
         <v>4011</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F48" s="4">
         <v>40001</v>
@@ -3937,10 +3945,10 @@
         <v>15</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K48" s="1">
         <v>22343</v>
@@ -3973,10 +3981,10 @@
         <v>4012</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F49" s="4">
         <v>40001</v>
@@ -3985,10 +3993,10 @@
         <v>15</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K49" s="1">
         <v>22823</v>
@@ -4021,10 +4029,10 @@
         <v>4013</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F50" s="4">
         <v>40003</v>
@@ -4033,10 +4041,10 @@
         <v>15</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K50" s="1">
         <v>15969</v>
@@ -4069,10 +4077,10 @@
         <v>4014</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F51" s="4">
         <v>40004</v>
@@ -4081,10 +4089,10 @@
         <v>15</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K51" s="1">
         <v>15161</v>
@@ -4117,10 +4125,10 @@
         <v>4015</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F52" s="4">
         <v>40006</v>
@@ -4129,10 +4137,10 @@
         <v>15</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K52" s="1">
         <v>28843</v>
@@ -4165,10 +4173,10 @@
         <v>4016</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F53" s="4">
         <v>40002</v>
@@ -4177,10 +4185,10 @@
         <v>15</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K53" s="1">
         <v>20397</v>
@@ -4213,10 +4221,10 @@
         <v>5001</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F54" s="4">
         <v>50001</v>
@@ -4225,7 +4233,7 @@
         <v>15</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K54" s="1">
         <v>231</v>
@@ -4258,10 +4266,10 @@
         <v>5002</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F55" s="4">
         <v>50002</v>
@@ -4270,10 +4278,10 @@
         <v>15</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K55" s="1">
         <v>15993</v>
@@ -4306,10 +4314,10 @@
         <v>5003</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F56" s="4">
         <v>50003</v>
@@ -4318,10 +4326,10 @@
         <v>15</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K56" s="1">
         <v>15110</v>
@@ -4354,10 +4362,10 @@
         <v>5004</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F57" s="4">
         <v>50004</v>
@@ -4366,10 +4374,10 @@
         <v>15</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K57" s="1">
         <v>14457</v>
@@ -4402,10 +4410,10 @@
         <v>5005</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F58" s="4">
         <v>50005</v>
@@ -4414,10 +4422,10 @@
         <v>15</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K58" s="1">
         <v>3289</v>
@@ -4450,10 +4458,10 @@
         <v>5006</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F59" s="4">
         <v>50006</v>
@@ -4462,10 +4470,10 @@
         <v>15</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K59" s="1">
         <v>38905</v>
@@ -4498,10 +4506,10 @@
         <v>5007</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F60" s="4">
         <v>50007</v>
@@ -4510,10 +4518,10 @@
         <v>15</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K60" s="1">
         <v>38443</v>
@@ -4546,10 +4554,10 @@
         <v>5011</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F61" s="4">
         <v>50001</v>
@@ -4558,10 +4566,10 @@
         <v>15</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K61" s="1">
         <v>7832</v>
@@ -4594,10 +4602,10 @@
         <v>5012</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F62" s="4">
         <v>50002</v>
@@ -4606,10 +4614,10 @@
         <v>15</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K62" s="1">
         <v>13618</v>
@@ -4642,10 +4650,10 @@
         <v>5013</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F63" s="4">
         <v>50003</v>
@@ -4654,10 +4662,10 @@
         <v>15</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K63" s="1">
         <v>14432</v>
@@ -4690,10 +4698,10 @@
         <v>5014</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F64" s="4">
         <v>50004</v>
@@ -4702,10 +4710,10 @@
         <v>15</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K64" s="1">
         <v>38484</v>
@@ -4738,10 +4746,10 @@
         <v>5015</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F65" s="4">
         <v>50005</v>
@@ -4750,10 +4758,10 @@
         <v>15</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K65" s="1">
         <v>-5260</v>
@@ -4786,10 +4794,10 @@
         <v>5016</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F66" s="4">
         <v>50006</v>
@@ -4798,10 +4806,10 @@
         <v>15</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K66" s="1">
         <v>6724</v>
